--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N148_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N148_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.01388364545168</v>
+        <v>3.089756092385898</v>
       </c>
       <c r="D2" t="n">
-        <v>36.07248581402532</v>
+        <v>5.861778944779115</v>
       </c>
       <c r="E2" t="n">
-        <v>17.87987467448816</v>
+        <v>2.905479634604326</v>
       </c>
       <c r="F2" t="n">
-        <v>18.91897897345155</v>
+        <v>3.074334083185877</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.52967427493598</v>
+        <v>3.336072069677097</v>
       </c>
       <c r="D3" t="n">
-        <v>29.5813999755484</v>
+        <v>4.806977496026615</v>
       </c>
       <c r="E3" t="n">
-        <v>17.87987467448816</v>
+        <v>2.905479634604326</v>
       </c>
       <c r="F3" t="n">
-        <v>18.91897897345155</v>
+        <v>3.074334083185877</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>27.87100146147751</v>
+        <v>4.529037737490095</v>
       </c>
       <c r="D4" t="n">
-        <v>3.940560476523232</v>
+        <v>0.6403410774350253</v>
       </c>
       <c r="E4" t="n">
-        <v>17.87987467448816</v>
+        <v>2.905479634604326</v>
       </c>
       <c r="F4" t="n">
-        <v>18.91897897345155</v>
+        <v>3.074334083185877</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>18.3363263713706</v>
+        <v>2.979653035347723</v>
       </c>
       <c r="D5" t="n">
-        <v>16.88916768406568</v>
+        <v>2.744489748660674</v>
       </c>
       <c r="E5" t="n">
-        <v>17.87987467448816</v>
+        <v>2.905479634604326</v>
       </c>
       <c r="F5" t="n">
-        <v>18.91897897345155</v>
+        <v>3.074334083185877</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>41.08606354998675</v>
+        <v>6.676485326872847</v>
       </c>
       <c r="D6" t="n">
-        <v>21.84373797885539</v>
+        <v>3.549607421564001</v>
       </c>
       <c r="E6" t="n">
-        <v>17.87987467448816</v>
+        <v>2.905479634604326</v>
       </c>
       <c r="F6" t="n">
-        <v>18.91897897345155</v>
+        <v>3.074334083185877</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>19.48560477956761</v>
+        <v>3.166410776679737</v>
       </c>
       <c r="D7" t="n">
-        <v>14.63915526423301</v>
+        <v>2.378862730437865</v>
       </c>
       <c r="E7" t="n">
-        <v>17.87987467448816</v>
+        <v>2.905479634604326</v>
       </c>
       <c r="F7" t="n">
-        <v>18.91897897345155</v>
+        <v>3.074334083185877</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>9.120310640676447</v>
+        <v>1.482050479109923</v>
       </c>
       <c r="D8" t="n">
-        <v>25.13798924365188</v>
+        <v>4.084923252093431</v>
       </c>
       <c r="E8" t="n">
-        <v>17.87987467448816</v>
+        <v>2.905479634604326</v>
       </c>
       <c r="F8" t="n">
-        <v>18.91897897345155</v>
+        <v>3.074334083185877</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>58.04813612335242</v>
+        <v>9.432822120044769</v>
       </c>
       <c r="D9" t="n">
-        <v>14.83516842581243</v>
+        <v>2.41071486919452</v>
       </c>
       <c r="E9" t="n">
-        <v>17.87987467448816</v>
+        <v>2.905479634604326</v>
       </c>
       <c r="F9" t="n">
-        <v>18.91897897345155</v>
+        <v>3.074334083185877</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>17.41849238018288</v>
+        <v>2.830505011779718</v>
       </c>
       <c r="D10" t="n">
-        <v>32.36117738138098</v>
+        <v>5.25869132447441</v>
       </c>
       <c r="E10" t="n">
-        <v>17.87987467448816</v>
+        <v>2.905479634604326</v>
       </c>
       <c r="F10" t="n">
-        <v>18.91897897345155</v>
+        <v>3.074334083185877</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>53.11119712523966</v>
+        <v>8.630569532851446</v>
       </c>
       <c r="D11" t="n">
-        <v>9.815109404018243</v>
+        <v>1.594955278152965</v>
       </c>
       <c r="E11" t="n">
-        <v>17.87987467448816</v>
+        <v>2.905479634604326</v>
       </c>
       <c r="F11" t="n">
-        <v>18.91897897345155</v>
+        <v>3.074334083185877</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>62.27952508073114</v>
+        <v>10.12042282561881</v>
       </c>
       <c r="D12" t="n">
-        <v>2.562533550965034</v>
+        <v>0.4164117020318181</v>
       </c>
       <c r="E12" t="n">
-        <v>17.87987467448816</v>
+        <v>2.905479634604326</v>
       </c>
       <c r="F12" t="n">
-        <v>18.91897897345155</v>
+        <v>3.074334083185877</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>69.39520678272044</v>
+        <v>11.27672110219207</v>
       </c>
       <c r="D13" t="n">
-        <v>7.666956516260026</v>
+        <v>1.245880433892254</v>
       </c>
       <c r="E13" t="n">
-        <v>17.87987467448816</v>
+        <v>2.905479634604326</v>
       </c>
       <c r="F13" t="n">
-        <v>18.91897897345155</v>
+        <v>3.074334083185877</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>33.27699021105614</v>
+        <v>5.407510909296624</v>
       </c>
       <c r="D14" t="n">
-        <v>51.76090445970477</v>
+        <v>8.411146974702024</v>
       </c>
       <c r="E14" t="n">
-        <v>17.87987467448816</v>
+        <v>2.905479634604326</v>
       </c>
       <c r="F14" t="n">
-        <v>18.91897897345155</v>
+        <v>3.074334083185877</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>32.15704891828071</v>
+        <v>5.225520449220615</v>
       </c>
       <c r="D15" t="n">
-        <v>49.8666587483973</v>
+        <v>8.103332046614561</v>
       </c>
       <c r="E15" t="n">
-        <v>17.87987467448816</v>
+        <v>2.905479634604326</v>
       </c>
       <c r="F15" t="n">
-        <v>18.91897897345155</v>
+        <v>3.074334083185877</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>45.50704432199989</v>
+        <v>7.394894702324983</v>
       </c>
       <c r="D16" t="n">
-        <v>64.12749152961328</v>
+        <v>10.42071737356216</v>
       </c>
       <c r="E16" t="n">
-        <v>17.87987467448816</v>
+        <v>2.905479634604326</v>
       </c>
       <c r="F16" t="n">
-        <v>18.91897897345155</v>
+        <v>3.074334083185877</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>48.06161275519472</v>
+        <v>7.810012072719141</v>
       </c>
       <c r="D17" t="n">
-        <v>56.41980098517575</v>
+        <v>9.168217660091061</v>
       </c>
       <c r="E17" t="n">
-        <v>17.87987467448816</v>
+        <v>2.905479634604326</v>
       </c>
       <c r="F17" t="n">
-        <v>18.91897897345155</v>
+        <v>3.074334083185877</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
